--- a/results/monthly_investor_report_2026-10-22.xlsx
+++ b/results/monthly_investor_report_2026-10-22.xlsx
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-24 06:36</t>
+          <t>Son Güncelleme: 2026-10-25 07:02</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-24 06:36</t>
+          <t>Son Güncelleme: 2026-10-25 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1913,7 +1913,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-24 06:36</t>
+          <t>Son Güncelleme: 2026-10-25 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2745,7 +2745,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-24 06:36</t>
+          <t>Son Güncelleme: 2026-10-25 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2864,7 +2864,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-24 06:36</t>
+          <t>Son Güncelleme: 2026-10-25 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3115,7 +3115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-24 06:36</t>
+          <t>Son Güncelleme: 2026-10-25 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3240,7 +3240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-24 06:36</t>
+          <t>Son Güncelleme: 2026-10-25 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3317,7 +3317,7 @@
         <v>-13277.62703984696</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>27933492.00133482</v>
+        <v>31863824.36463429</v>
       </c>
       <c r="H4" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3347,7 +3347,7 @@
         <v>-8144.448949737256</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>27933492.00133482</v>
+        <v>31863824.36463429</v>
       </c>
       <c r="H5" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3377,7 +3377,7 @@
         <v>-627601.611911966</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>27933492.00133482</v>
+        <v>31863824.36463429</v>
       </c>
       <c r="H6" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3407,7 +3407,7 @@
         <v>-815594.0330395401</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>27933492.00133482</v>
+        <v>31863824.36463429</v>
       </c>
       <c r="H7" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>27933492.00133482</v>
+        <v>31863824.36463429</v>
       </c>
       <c r="H8" s="30" t="n">
         <v>-0.1812317286467454</v>

--- a/results/monthly_investor_report_2026-10-22.xlsx
+++ b/results/monthly_investor_report_2026-10-22.xlsx
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-25 07:02</t>
+          <t>Son Güncelleme: 2026-10-26 07:09</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-25 07:02</t>
+          <t>Son Güncelleme: 2026-10-26 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1913,7 +1913,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-25 07:02</t>
+          <t>Son Güncelleme: 2026-10-26 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2745,7 +2745,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-25 07:02</t>
+          <t>Son Güncelleme: 2026-10-26 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2864,7 +2864,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-25 07:02</t>
+          <t>Son Güncelleme: 2026-10-26 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3115,7 +3115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-25 07:02</t>
+          <t>Son Güncelleme: 2026-10-26 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3240,7 +3240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-25 07:02</t>
+          <t>Son Güncelleme: 2026-10-26 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3317,7 +3317,7 @@
         <v>-13277.62703984696</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>31863824.36463429</v>
+        <v>35794156.72793375</v>
       </c>
       <c r="H4" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3347,7 +3347,7 @@
         <v>-8144.448949737256</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>31863824.36463429</v>
+        <v>35794156.72793375</v>
       </c>
       <c r="H5" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3377,7 +3377,7 @@
         <v>-627601.611911966</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>31863824.36463429</v>
+        <v>35794156.72793375</v>
       </c>
       <c r="H6" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3407,7 +3407,7 @@
         <v>-815594.0330395401</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>31863824.36463429</v>
+        <v>35794156.72793375</v>
       </c>
       <c r="H7" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>31863824.36463429</v>
+        <v>35794156.72793375</v>
       </c>
       <c r="H8" s="30" t="n">
         <v>-0.1812317286467454</v>
